--- a/youzi/浙江帮/index.xlsx
+++ b/youzi/浙江帮/index.xlsx
@@ -39,13 +39,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF78C88A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,25 +135,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,31 +261,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,73 +339,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,115 +375,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -399,144 +477,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -562,6 +502,66 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>603271</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="7" t="str">
         <v>净卖: -611.78万</v>
       </c>
       <c r="E2">
@@ -1833,40 +1833,40 @@
       <c r="H2">
         <v>-0.7</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="8">
         <v>1.59</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="1">
         <v>0</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="11">
         <v>-0.49</v>
       </c>
       <c r="L2" s="9">
         <v>-3.9</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="2">
         <v>-5.73</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="3">
         <v>-5.34</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="4">
         <v>-4.71</v>
       </c>
       <c r="P2" s="6">
         <v>-5.39</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="10">
         <v>-3.12</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="5">
         <v>-2.73</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="12">
         <v>-3.56</v>
       </c>
-      <c r="T2" s="12">
+      <c r="T2" s="13">
         <v>23.29</v>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>000802</v>
       </c>
-      <c r="D3" s="14" t="str">
+      <c r="D3" s="15" t="str">
         <v>净买: 215.00万</v>
       </c>
       <c r="E3">
@@ -1895,40 +1895,40 @@
       <c r="H3">
         <v>-10.05</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="16">
         <v>0</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="17">
         <v>-3.35</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="18">
         <v>-6.33</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="25">
         <v>-9.68</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="19">
         <v>-9.5</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="22">
         <v>-7.45</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="26">
         <v>-7.45</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="20">
         <v>-7.26</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="23">
         <v>-7.08</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="24">
         <v>-7.82</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="14">
         <v>-7.82</v>
       </c>
-      <c r="T3" s="23">
+      <c r="T3" s="21">
         <v>-26.26</v>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300192</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="37" t="str">
         <v>净卖: -647.70万</v>
       </c>
       <c r="E4">
@@ -1957,40 +1957,40 @@
       <c r="H4">
         <v>20.01</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="30">
         <v>0</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="33">
         <v>1.58</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="34">
         <v>-8.92</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="38">
         <v>-6.87</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="31">
         <v>-15.82</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="32">
         <v>-18.33</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="39">
         <v>-20.76</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="35">
         <v>-23.43</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="27">
         <v>-23.39</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="28">
         <v>-23.85</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="36">
         <v>-24.62</v>
       </c>
-      <c r="T4" s="37">
+      <c r="T4" s="29">
         <v>-20.92</v>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>605028</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="50" t="str">
         <v>净买: 256.97万</v>
       </c>
       <c r="E5">
@@ -2019,40 +2019,40 @@
       <c r="H5">
         <v>-0.68</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="44">
         <v>-9.39</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="48">
         <v>-13.51</v>
       </c>
       <c r="K5" s="49">
         <v>-15.6</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="51">
         <v>-16.09</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="45">
         <v>-10.3</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="52">
         <v>-10.1</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="40">
         <v>-12.26</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="42">
         <v>-12.39</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="41">
         <v>-11.58</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="46">
         <v>-12.62</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="47">
         <v>-13.28</v>
       </c>
-      <c r="T5" s="47">
+      <c r="T5" s="43">
         <v>-8.96</v>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000722</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="56" t="str">
         <v>净卖: -6181.92万</v>
       </c>
       <c r="E6">
@@ -2081,40 +2081,40 @@
       <c r="H6">
         <v>6.98</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="63">
         <v>2.81</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="58">
         <v>-4.61</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="64">
         <v>-11.64</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="59">
         <v>-17.83</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="60">
         <v>-21.09</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="61">
         <v>-23.12</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="62">
         <v>-28.29</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="57">
         <v>-27.67</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="65">
         <v>-26.72</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="53">
         <v>-28.8</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="54">
         <v>-26.94</v>
       </c>
-      <c r="T6" s="60">
+      <c r="T6" s="55">
         <v>-24.58</v>
       </c>
     </row>
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="74">
+      <c r="I8" s="66">
         <v>40</v>
       </c>
-      <c r="J8" s="75">
+      <c r="J8" s="73">
         <v>20</v>
       </c>
       <c r="K8" s="67">
         <v>0</v>
       </c>
-      <c r="L8" s="76">
+      <c r="L8" s="68">
         <v>0</v>
       </c>
       <c r="M8" s="69">
         <v>0</v>
       </c>
-      <c r="N8" s="70">
+      <c r="N8" s="75">
         <v>0</v>
       </c>
-      <c r="O8" s="77">
+      <c r="O8" s="70">
         <v>0</v>
       </c>
-      <c r="P8" s="68">
+      <c r="P8" s="76">
         <v>0</v>
       </c>
-      <c r="Q8" s="71">
+      <c r="Q8" s="77">
         <v>0</v>
       </c>
-      <c r="R8" s="66">
+      <c r="R8" s="71">
         <v>0</v>
       </c>
       <c r="S8" s="72">
         <v>0</v>
       </c>
-      <c r="T8" s="73">
+      <c r="T8" s="74">
         <v>20</v>
       </c>
     </row>
@@ -2225,40 +2225,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="88">
+      <c r="I9" s="78">
         <v>-1</v>
       </c>
       <c r="J9" s="81">
         <v>-3.98</v>
       </c>
-      <c r="K9" s="89">
+      <c r="K9" s="82">
         <v>-8.6</v>
       </c>
-      <c r="L9" s="78">
+      <c r="L9" s="86">
         <v>-10.87</v>
       </c>
-      <c r="M9" s="84">
+      <c r="M9" s="87">
         <v>-12.49</v>
       </c>
-      <c r="N9" s="85">
+      <c r="N9" s="88">
         <v>-12.87</v>
       </c>
-      <c r="O9" s="82">
+      <c r="O9" s="79">
         <v>-14.69</v>
       </c>
-      <c r="P9" s="83">
+      <c r="P9" s="84">
         <v>-15.23</v>
       </c>
-      <c r="Q9" s="80">
+      <c r="Q9" s="85">
         <v>-14.38</v>
       </c>
-      <c r="R9" s="79">
+      <c r="R9" s="89">
         <v>-15.16</v>
       </c>
-      <c r="S9" s="86">
+      <c r="S9" s="83">
         <v>-15.24</v>
       </c>
-      <c r="T9" s="87">
+      <c r="T9" s="80">
         <v>-11.49</v>
       </c>
     </row>

--- a/youzi/浙江帮/index.xlsx
+++ b/youzi/浙江帮/index.xlsx
@@ -45,6 +45,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF259E41"/>
         <bgColor/>
       </patternFill>
@@ -57,19 +87,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF34AC4F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF89CE99"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,43 +273,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,109 +285,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,6 +315,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -261,79 +375,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -381,102 +501,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -502,30 +526,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>603271</v>
       </c>
-      <c r="D2" s="7" t="str">
+      <c r="D2" s="5" t="str">
         <v>净卖: -611.78万</v>
       </c>
       <c r="E2">
@@ -1833,40 +1833,40 @@
       <c r="H2">
         <v>-0.7</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="9">
         <v>1.59</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="10">
         <v>-0.49</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="6">
         <v>-3.9</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="7">
         <v>-5.73</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="8">
         <v>-5.34</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="11">
         <v>-4.71</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="12">
         <v>-5.39</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="2">
         <v>-3.12</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="13">
         <v>-2.73</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="3">
         <v>-3.56</v>
       </c>
-      <c r="T2" s="13">
+      <c r="T2" s="4">
         <v>23.29</v>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>000802</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="24" t="str">
         <v>净买: 215.00万</v>
       </c>
       <c r="E3">
@@ -1898,22 +1898,22 @@
       <c r="I3" s="16">
         <v>0</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="25">
         <v>-3.35</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="26">
         <v>-6.33</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="14">
         <v>-9.68</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="15">
         <v>-9.5</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="19">
         <v>-7.45</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="17">
         <v>-7.45</v>
       </c>
       <c r="P3" s="20">
@@ -1922,13 +1922,13 @@
       <c r="Q3" s="23">
         <v>-7.08</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="21">
         <v>-7.82</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="22">
         <v>-7.82</v>
       </c>
-      <c r="T3" s="21">
+      <c r="T3" s="18">
         <v>-26.26</v>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300192</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="39" t="str">
         <v>净卖: -647.70万</v>
       </c>
       <c r="E4">
@@ -1957,40 +1957,40 @@
       <c r="H4">
         <v>20.01</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="37">
         <v>0</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="29">
         <v>1.58</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="33">
         <v>-8.92</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="34">
         <v>-6.87</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="30">
         <v>-15.82</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="31">
         <v>-18.33</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="27">
         <v>-20.76</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="38">
         <v>-23.43</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="35">
         <v>-23.39</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="32">
         <v>-23.85</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="28">
         <v>-24.62</v>
       </c>
-      <c r="T4" s="29">
+      <c r="T4" s="36">
         <v>-20.92</v>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>605028</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="41" t="str">
         <v>净买: 256.97万</v>
       </c>
       <c r="E5">
@@ -2019,40 +2019,40 @@
       <c r="H5">
         <v>-0.68</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="47">
         <v>-9.39</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="50">
         <v>-13.51</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="48">
         <v>-15.6</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="42">
         <v>-16.09</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="52">
         <v>-10.3</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="49">
         <v>-10.1</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="43">
         <v>-12.26</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="40">
         <v>-12.39</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="44">
         <v>-11.58</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="45">
         <v>-12.62</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="51">
         <v>-13.28</v>
       </c>
-      <c r="T5" s="43">
+      <c r="T5" s="46">
         <v>-8.96</v>
       </c>
     </row>
@@ -2081,40 +2081,40 @@
       <c r="H6">
         <v>6.98</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="60">
         <v>2.81</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="61">
         <v>-4.61</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="65">
         <v>-11.64</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="57">
         <v>-17.83</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="53">
         <v>-21.09</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="54">
         <v>-23.12</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="58">
         <v>-28.29</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="63">
         <v>-27.67</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="62">
         <v>-26.72</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="59">
         <v>-28.8</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="55">
         <v>-26.94</v>
       </c>
-      <c r="T6" s="55">
+      <c r="T6" s="64">
         <v>-24.58</v>
       </c>
     </row>
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="66">
+      <c r="I8" s="76">
         <v>40</v>
       </c>
-      <c r="J8" s="73">
+      <c r="J8" s="71">
         <v>20</v>
       </c>
-      <c r="K8" s="67">
+      <c r="K8" s="77">
         <v>0</v>
       </c>
-      <c r="L8" s="68">
+      <c r="L8" s="74">
         <v>0</v>
       </c>
-      <c r="M8" s="69">
+      <c r="M8" s="67">
         <v>0</v>
       </c>
-      <c r="N8" s="75">
+      <c r="N8" s="72">
         <v>0</v>
       </c>
-      <c r="O8" s="70">
+      <c r="O8" s="73">
         <v>0</v>
       </c>
-      <c r="P8" s="76">
+      <c r="P8" s="68">
         <v>0</v>
       </c>
-      <c r="Q8" s="77">
+      <c r="Q8" s="69">
         <v>0</v>
       </c>
-      <c r="R8" s="71">
+      <c r="R8" s="70">
         <v>0</v>
       </c>
-      <c r="S8" s="72">
+      <c r="S8" s="66">
         <v>0</v>
       </c>
-      <c r="T8" s="74">
+      <c r="T8" s="75">
         <v>20</v>
       </c>
     </row>
@@ -2225,40 +2225,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="78">
+      <c r="I9" s="82">
         <v>-1</v>
       </c>
-      <c r="J9" s="81">
+      <c r="J9" s="83">
         <v>-3.98</v>
       </c>
-      <c r="K9" s="82">
+      <c r="K9" s="80">
         <v>-8.6</v>
       </c>
-      <c r="L9" s="86">
+      <c r="L9" s="84">
         <v>-10.87</v>
       </c>
-      <c r="M9" s="87">
+      <c r="M9" s="85">
         <v>-12.49</v>
       </c>
-      <c r="N9" s="88">
+      <c r="N9" s="81">
         <v>-12.87</v>
       </c>
-      <c r="O9" s="79">
+      <c r="O9" s="78">
         <v>-14.69</v>
       </c>
-      <c r="P9" s="84">
+      <c r="P9" s="87">
         <v>-15.23</v>
       </c>
-      <c r="Q9" s="85">
+      <c r="Q9" s="88">
         <v>-14.38</v>
       </c>
-      <c r="R9" s="89">
+      <c r="R9" s="79">
         <v>-15.16</v>
       </c>
-      <c r="S9" s="83">
+      <c r="S9" s="86">
         <v>-15.24</v>
       </c>
-      <c r="T9" s="80">
+      <c r="T9" s="89">
         <v>-11.49</v>
       </c>
     </row>

--- a/youzi/浙江帮/index.xlsx
+++ b/youzi/浙江帮/index.xlsx
@@ -39,25 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF65C07A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF26A243"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,49 +117,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,49 +153,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF208A39"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,79 +315,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,60 +417,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -393,103 +477,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -526,6 +520,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>603271</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="13" t="str">
         <v>净卖: -611.78万</v>
       </c>
       <c r="E2">
@@ -1836,38 +1836,38 @@
       <c r="I2" s="9">
         <v>1.59</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="10">
         <v>0</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="4">
         <v>-0.49</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>-3.9</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="6">
         <v>-5.73</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="12">
         <v>-5.34</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="7">
         <v>-4.71</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="1">
         <v>-5.39</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="8">
         <v>-3.12</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="2">
         <v>-2.73</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="11">
         <v>-3.56</v>
       </c>
-      <c r="T2" s="4">
-        <v>23.29</v>
+      <c r="T2" s="3">
+        <v>24.41</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>000802</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="16" t="str">
         <v>净买: 215.00万</v>
       </c>
       <c r="E3">
@@ -1895,25 +1895,25 @@
       <c r="H3">
         <v>-10.05</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="24">
         <v>0</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="17">
         <v>-3.35</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="25">
         <v>-6.33</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="18">
         <v>-9.68</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="19">
         <v>-9.5</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="26">
         <v>-7.45</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="14">
         <v>-7.45</v>
       </c>
       <c r="P3" s="20">
@@ -1928,8 +1928,8 @@
       <c r="S3" s="22">
         <v>-7.82</v>
       </c>
-      <c r="T3" s="18">
-        <v>-26.26</v>
+      <c r="T3" s="15">
+        <v>-24.58</v>
       </c>
     </row>
     <row r="4">
@@ -1957,41 +1957,41 @@
       <c r="H4">
         <v>20.01</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="36">
         <v>0</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="32">
         <v>1.58</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="27">
         <v>-8.92</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="33">
         <v>-6.87</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="34">
         <v>-15.82</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="37">
         <v>-18.33</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="28">
         <v>-20.76</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="35">
         <v>-23.43</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="29">
         <v>-23.39</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="30">
         <v>-23.85</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="31">
         <v>-24.62</v>
       </c>
-      <c r="T4" s="36">
-        <v>-20.92</v>
+      <c r="T4" s="38">
+        <v>-22.69</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>605028</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="46" t="str">
         <v>净买: 256.97万</v>
       </c>
       <c r="E5">
@@ -2022,38 +2022,38 @@
       <c r="I5" s="47">
         <v>-9.39</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="51">
         <v>-13.51</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="52">
         <v>-15.6</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="50">
         <v>-16.09</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="40">
         <v>-10.3</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="43">
         <v>-10.1</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="41">
         <v>-12.26</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="48">
         <v>-12.39</v>
       </c>
       <c r="Q5" s="44">
         <v>-11.58</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="49">
         <v>-12.62</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="42">
         <v>-13.28</v>
       </c>
-      <c r="T5" s="46">
-        <v>-8.96</v>
+      <c r="T5" s="45">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000722</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="62" t="str">
         <v>净卖: -6181.92万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>6.98</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="55">
         <v>2.81</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="56">
         <v>-4.61</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="59">
         <v>-11.64</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="54">
         <v>-17.83</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="60">
         <v>-21.09</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="63">
         <v>-23.12</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="64">
         <v>-28.29</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="57">
         <v>-27.67</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="65">
         <v>-26.72</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="58">
         <v>-28.8</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="61">
         <v>-26.94</v>
       </c>
-      <c r="T6" s="64">
-        <v>-24.58</v>
+      <c r="T6" s="53">
+        <v>-22.95</v>
       </c>
     </row>
     <row r="7">
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="76">
+      <c r="I8" s="70">
         <v>40</v>
       </c>
-      <c r="J8" s="71">
+      <c r="J8" s="73">
         <v>20</v>
       </c>
-      <c r="K8" s="77">
+      <c r="K8" s="71">
         <v>0</v>
       </c>
-      <c r="L8" s="74">
+      <c r="L8" s="77">
         <v>0</v>
       </c>
-      <c r="M8" s="67">
+      <c r="M8" s="66">
         <v>0</v>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="74">
         <v>0</v>
       </c>
-      <c r="O8" s="73">
+      <c r="O8" s="72">
         <v>0</v>
       </c>
-      <c r="P8" s="68">
+      <c r="P8" s="67">
         <v>0</v>
       </c>
-      <c r="Q8" s="69">
+      <c r="Q8" s="68">
         <v>0</v>
       </c>
-      <c r="R8" s="70">
+      <c r="R8" s="75">
         <v>0</v>
       </c>
-      <c r="S8" s="66">
+      <c r="S8" s="69">
         <v>0</v>
       </c>
-      <c r="T8" s="75">
+      <c r="T8" s="76">
         <v>20</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="82">
+      <c r="I9" s="81">
         <v>-1</v>
       </c>
-      <c r="J9" s="83">
+      <c r="J9" s="85">
         <v>-3.98</v>
       </c>
-      <c r="K9" s="80">
+      <c r="K9" s="87">
         <v>-8.6</v>
       </c>
-      <c r="L9" s="84">
+      <c r="L9" s="88">
         <v>-10.87</v>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="82">
         <v>-12.49</v>
       </c>
-      <c r="N9" s="81">
+      <c r="N9" s="86">
         <v>-12.87</v>
       </c>
       <c r="O9" s="78">
         <v>-14.69</v>
       </c>
-      <c r="P9" s="87">
+      <c r="P9" s="83">
         <v>-15.23</v>
       </c>
-      <c r="Q9" s="88">
+      <c r="Q9" s="84">
         <v>-14.38</v>
       </c>
       <c r="R9" s="79">
         <v>-15.16</v>
       </c>
-      <c r="S9" s="86">
+      <c r="S9" s="89">
         <v>-15.24</v>
       </c>
-      <c r="T9" s="89">
-        <v>-11.49</v>
+      <c r="T9" s="80">
+        <v>-9.64</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/浙江帮/index.xlsx
+++ b/youzi/浙江帮/index.xlsx
@@ -39,13 +39,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF26A243"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
+        <fgColor rgb="FFE9F6EC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,19 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
+        <fgColor rgb="FF26A243"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,13 +117,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,13 +171,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,7 +201,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,121 +339,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,96 +393,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF38AD53"/>
         <bgColor/>
       </patternFill>
@@ -405,6 +429,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -435,91 +513,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>603271</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -611.78万</v>
       </c>
       <c r="E2">
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>-0.7</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="7">
         <v>1.59</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="8">
         <v>0</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="10">
         <v>-0.49</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <v>-3.9</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="5">
         <v>-5.73</v>
       </c>
       <c r="N2" s="12">
         <v>-5.34</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="13">
         <v>-4.71</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="9">
         <v>-5.39</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="6">
         <v>-3.12</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="1">
         <v>-2.73</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="2">
         <v>-3.56</v>
       </c>
-      <c r="T2" s="3">
-        <v>24.41</v>
+      <c r="T2" s="11">
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>000802</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="15" t="str">
         <v>净买: 215.00万</v>
       </c>
       <c r="E3">
@@ -1895,41 +1895,41 @@
       <c r="H3">
         <v>-10.05</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="22">
         <v>0</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="16">
         <v>-3.35</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="24">
         <v>-6.33</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="23">
         <v>-9.68</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="25">
         <v>-9.5</v>
       </c>
       <c r="N3" s="26">
         <v>-7.45</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="17">
         <v>-7.45</v>
       </c>
       <c r="P3" s="20">
         <v>-7.26</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="21">
         <v>-7.08</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="18">
         <v>-7.82</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="14">
         <v>-7.82</v>
       </c>
-      <c r="T3" s="15">
-        <v>-24.58</v>
+      <c r="T3" s="19">
+        <v>-16.95</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300192</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="27" t="str">
         <v>净卖: -647.70万</v>
       </c>
       <c r="E4">
@@ -1963,35 +1963,35 @@
       <c r="J4" s="32">
         <v>1.58</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="33">
         <v>-8.92</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="37">
         <v>-6.87</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="28">
         <v>-15.82</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="29">
         <v>-18.33</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="34">
         <v>-20.76</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="38">
         <v>-23.43</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="35">
         <v>-23.39</v>
       </c>
       <c r="R4" s="30">
         <v>-23.85</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="39">
         <v>-24.62</v>
       </c>
-      <c r="T4" s="38">
-        <v>-22.69</v>
+      <c r="T4" s="31">
+        <v>-23.47</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>605028</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="50" t="str">
         <v>净买: 256.97万</v>
       </c>
       <c r="E5">
@@ -2019,40 +2019,40 @@
       <c r="H5">
         <v>-0.68</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="46">
         <v>-9.39</v>
       </c>
       <c r="J5" s="51">
         <v>-13.51</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="47">
         <v>-15.6</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="43">
         <v>-16.09</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="52">
         <v>-10.3</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="44">
         <v>-10.1</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="49">
         <v>-12.26</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="40">
         <v>-12.39</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="41">
         <v>-11.58</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="45">
         <v>-12.62</v>
       </c>
       <c r="S5" s="42">
         <v>-13.28</v>
       </c>
-      <c r="T5" s="45">
+      <c r="T5" s="48">
         <v>-2.39</v>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000722</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="58" t="str">
         <v>净卖: -6181.92万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>6.98</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="53">
         <v>2.81</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="60">
         <v>-4.61</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="61">
         <v>-11.64</v>
       </c>
       <c r="L6" s="54">
         <v>-17.83</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="55">
         <v>-21.09</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="59">
         <v>-23.12</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="62">
         <v>-28.29</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="56">
         <v>-27.67</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="63">
         <v>-26.72</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="64">
         <v>-28.8</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="57">
         <v>-26.94</v>
       </c>
-      <c r="T6" s="53">
-        <v>-22.95</v>
+      <c r="T6" s="65">
+        <v>-21.65</v>
       </c>
     </row>
     <row r="7">
@@ -2177,13 +2177,13 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="70">
+      <c r="I8" s="75">
         <v>40</v>
       </c>
-      <c r="J8" s="73">
+      <c r="J8" s="69">
         <v>20</v>
       </c>
-      <c r="K8" s="71">
+      <c r="K8" s="76">
         <v>0</v>
       </c>
       <c r="L8" s="77">
@@ -2192,25 +2192,25 @@
       <c r="M8" s="66">
         <v>0</v>
       </c>
-      <c r="N8" s="74">
+      <c r="N8" s="67">
         <v>0</v>
       </c>
-      <c r="O8" s="72">
+      <c r="O8" s="70">
         <v>0</v>
       </c>
-      <c r="P8" s="67">
+      <c r="P8" s="71">
         <v>0</v>
       </c>
       <c r="Q8" s="68">
         <v>0</v>
       </c>
-      <c r="R8" s="75">
+      <c r="R8" s="72">
         <v>0</v>
       </c>
-      <c r="S8" s="69">
+      <c r="S8" s="73">
         <v>0</v>
       </c>
-      <c r="T8" s="76">
+      <c r="T8" s="74">
         <v>20</v>
       </c>
     </row>
@@ -2225,10 +2225,10 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="81">
+      <c r="I9" s="80">
         <v>-1</v>
       </c>
-      <c r="J9" s="85">
+      <c r="J9" s="86">
         <v>-3.98</v>
       </c>
       <c r="K9" s="87">
@@ -2237,29 +2237,29 @@
       <c r="L9" s="88">
         <v>-10.87</v>
       </c>
-      <c r="M9" s="82">
+      <c r="M9" s="89">
         <v>-12.49</v>
       </c>
-      <c r="N9" s="86">
+      <c r="N9" s="81">
         <v>-12.87</v>
       </c>
-      <c r="O9" s="78">
+      <c r="O9" s="82">
         <v>-14.69</v>
       </c>
-      <c r="P9" s="83">
+      <c r="P9" s="78">
         <v>-15.23</v>
       </c>
-      <c r="Q9" s="84">
+      <c r="Q9" s="83">
         <v>-14.38</v>
       </c>
-      <c r="R9" s="79">
+      <c r="R9" s="84">
         <v>-15.16</v>
       </c>
-      <c r="S9" s="89">
+      <c r="S9" s="79">
         <v>-15.24</v>
       </c>
-      <c r="T9" s="80">
-        <v>-9.64</v>
+      <c r="T9" s="85">
+        <v>-7.89</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/浙江帮/index.xlsx
+++ b/youzi/浙江帮/index.xlsx
@@ -39,13 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF89CE99"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,25 +117,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,37 +189,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,67 +291,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,157 +417,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -393,97 +483,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -514,60 +568,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>603271</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="13" t="str">
         <v>净卖: -611.78万</v>
       </c>
       <c r="E2">
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>-0.7</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="1">
         <v>1.59</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="3">
         <v>-0.49</v>
       </c>
       <c r="L2" s="4">
         <v>-3.9</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="10">
         <v>-5.73</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="5">
         <v>-5.34</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="11">
         <v>-4.71</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="7">
         <v>-5.39</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="12">
         <v>-3.12</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="8">
         <v>-2.73</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="6">
         <v>-3.56</v>
       </c>
-      <c r="T2" s="11">
-        <v>25</v>
+      <c r="T2" s="9">
+        <v>21.41</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>000802</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="19" t="str">
         <v>净买: 215.00万</v>
       </c>
       <c r="E3">
@@ -1895,41 +1895,41 @@
       <c r="H3">
         <v>-10.05</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="25">
         <v>0</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="20">
         <v>-3.35</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="26">
         <v>-6.33</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="14">
         <v>-9.68</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="21">
         <v>-9.5</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="23">
         <v>-7.45</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="24">
         <v>-7.45</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="15">
         <v>-7.26</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="16">
         <v>-7.08</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="17">
         <v>-7.82</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="18">
         <v>-7.82</v>
       </c>
-      <c r="T3" s="19">
-        <v>-16.95</v>
+      <c r="T3" s="22">
+        <v>-24.02</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300192</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="39" t="str">
         <v>净卖: -647.70万</v>
       </c>
       <c r="E4">
@@ -1957,41 +1957,41 @@
       <c r="H4">
         <v>20.01</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="34">
         <v>0</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="35">
         <v>1.58</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="31">
         <v>-8.92</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="32">
         <v>-6.87</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="27">
         <v>-15.82</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="36">
         <v>-18.33</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="28">
         <v>-20.76</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="37">
         <v>-23.43</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="33">
         <v>-23.39</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="29">
         <v>-23.85</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="38">
         <v>-24.62</v>
       </c>
-      <c r="T4" s="31">
-        <v>-23.47</v>
+      <c r="T4" s="30">
+        <v>-25.24</v>
       </c>
     </row>
     <row r="5">
@@ -1999,12 +1999,12 @@
         <v>2025-10-09</v>
       </c>
       <c r="B5" t="str">
-        <v>世茂能源</v>
+        <v>XD世茂能</v>
       </c>
       <c r="C5" t="str">
         <v>605028</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="42" t="str">
         <v>净买: 256.97万</v>
       </c>
       <c r="E5">
@@ -2019,25 +2019,25 @@
       <c r="H5">
         <v>-0.68</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="50">
         <v>-9.39</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="43">
         <v>-13.51</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="46">
         <v>-15.6</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="47">
         <v>-16.09</v>
       </c>
       <c r="M5" s="52">
         <v>-10.3</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="48">
         <v>-10.1</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="44">
         <v>-12.26</v>
       </c>
       <c r="P5" s="40">
@@ -2046,14 +2046,14 @@
       <c r="Q5" s="41">
         <v>-11.58</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="51">
         <v>-12.62</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="45">
         <v>-13.28</v>
       </c>
-      <c r="T5" s="48">
-        <v>-2.39</v>
+      <c r="T5" s="49">
+        <v>-3.96</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000722</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -6181.92万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>6.98</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="56">
         <v>2.81</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="64">
         <v>-4.61</v>
       </c>
       <c r="K6" s="61">
         <v>-11.64</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="65">
         <v>-17.83</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="53">
         <v>-21.09</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="57">
         <v>-23.12</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="59">
         <v>-28.29</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="62">
         <v>-27.67</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="54">
         <v>-26.72</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="55">
         <v>-28.8</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="58">
         <v>-26.94</v>
       </c>
-      <c r="T6" s="65">
-        <v>-21.65</v>
+      <c r="T6" s="60">
+        <v>-18.17</v>
       </c>
     </row>
     <row r="7">
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="75">
+      <c r="I8" s="73">
         <v>40</v>
       </c>
-      <c r="J8" s="69">
+      <c r="J8" s="66">
         <v>20</v>
       </c>
-      <c r="K8" s="76">
+      <c r="K8" s="67">
         <v>0</v>
       </c>
-      <c r="L8" s="77">
+      <c r="L8" s="68">
         <v>0</v>
       </c>
-      <c r="M8" s="66">
+      <c r="M8" s="70">
         <v>0</v>
       </c>
-      <c r="N8" s="67">
+      <c r="N8" s="76">
         <v>0</v>
       </c>
-      <c r="O8" s="70">
+      <c r="O8" s="74">
         <v>0</v>
       </c>
       <c r="P8" s="71">
         <v>0</v>
       </c>
-      <c r="Q8" s="68">
+      <c r="Q8" s="72">
         <v>0</v>
       </c>
-      <c r="R8" s="72">
+      <c r="R8" s="75">
         <v>0</v>
       </c>
-      <c r="S8" s="73">
+      <c r="S8" s="77">
         <v>0</v>
       </c>
-      <c r="T8" s="74">
+      <c r="T8" s="69">
         <v>20</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="80">
+      <c r="I9" s="89">
         <v>-1</v>
       </c>
-      <c r="J9" s="86">
+      <c r="J9" s="78">
         <v>-3.98</v>
       </c>
-      <c r="K9" s="87">
+      <c r="K9" s="82">
         <v>-8.6</v>
       </c>
-      <c r="L9" s="88">
+      <c r="L9" s="87">
         <v>-10.87</v>
       </c>
-      <c r="M9" s="89">
+      <c r="M9" s="83">
         <v>-12.49</v>
       </c>
-      <c r="N9" s="81">
+      <c r="N9" s="88">
         <v>-12.87</v>
       </c>
-      <c r="O9" s="82">
+      <c r="O9" s="84">
         <v>-14.69</v>
       </c>
-      <c r="P9" s="78">
+      <c r="P9" s="79">
         <v>-15.23</v>
       </c>
-      <c r="Q9" s="83">
+      <c r="Q9" s="80">
         <v>-14.38</v>
       </c>
-      <c r="R9" s="84">
+      <c r="R9" s="85">
         <v>-15.16</v>
       </c>
-      <c r="S9" s="79">
+      <c r="S9" s="81">
         <v>-15.24</v>
       </c>
-      <c r="T9" s="85">
-        <v>-7.89</v>
+      <c r="T9" s="86">
+        <v>-10</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/浙江帮/index.xlsx
+++ b/youzi/浙江帮/index.xlsx
@@ -39,73 +39,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF3BEC3"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,31 +213,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,97 +315,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,84 +369,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -375,6 +381,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -417,78 +459,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -568,6 +538,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>-0.7</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="12">
         <v>1.59</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>0</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="8">
         <v>-0.49</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="5">
         <v>-3.9</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="6">
         <v>-5.73</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="2">
         <v>-5.34</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="9">
         <v>-4.71</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="10">
         <v>-5.39</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="7">
         <v>-3.12</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="11">
         <v>-2.73</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="3">
         <v>-3.56</v>
       </c>
-      <c r="T2" s="9">
-        <v>21.41</v>
+      <c r="T2" s="4">
+        <v>24.17</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>000802</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="26" t="str">
         <v>净买: 215.00万</v>
       </c>
       <c r="E3">
@@ -1895,41 +1895,41 @@
       <c r="H3">
         <v>-10.05</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="22">
         <v>0</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="14">
         <v>-3.35</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="15">
         <v>-6.33</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="16">
         <v>-9.68</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="17">
         <v>-9.5</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="24">
         <v>-7.45</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="23">
         <v>-7.45</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="19">
         <v>-7.26</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="18">
         <v>-7.08</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="20">
         <v>-7.82</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="21">
         <v>-7.82</v>
       </c>
-      <c r="T3" s="22">
-        <v>-24.02</v>
+      <c r="T3" s="25">
+        <v>-19.93</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300192</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -647.70万</v>
       </c>
       <c r="E4">
@@ -1963,35 +1963,35 @@
       <c r="J4" s="35">
         <v>1.58</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="37">
         <v>-8.92</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="36">
         <v>-6.87</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="39">
         <v>-15.82</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="30">
         <v>-18.33</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="27">
         <v>-20.76</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="31">
         <v>-23.43</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="28">
         <v>-23.39</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="38">
         <v>-23.85</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="32">
         <v>-24.62</v>
       </c>
-      <c r="T4" s="30">
-        <v>-25.24</v>
+      <c r="T4" s="33">
+        <v>-24.35</v>
       </c>
     </row>
     <row r="5">
@@ -1999,12 +1999,12 @@
         <v>2025-10-09</v>
       </c>
       <c r="B5" t="str">
-        <v>XD世茂能</v>
+        <v>世茂能源</v>
       </c>
       <c r="C5" t="str">
         <v>605028</v>
       </c>
-      <c r="D5" s="42" t="str">
+      <c r="D5" s="46" t="str">
         <v>净买: 256.97万</v>
       </c>
       <c r="E5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>-0.68</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="47">
         <v>-9.39</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="42">
         <v>-13.51</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="43">
         <v>-15.6</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="50">
         <v>-16.09</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="44">
         <v>-10.3</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="51">
         <v>-10.1</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="52">
         <v>-12.26</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="48">
         <v>-12.39</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="40">
         <v>-11.58</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="49">
         <v>-12.62</v>
       </c>
       <c r="S5" s="45">
         <v>-13.28</v>
       </c>
-      <c r="T5" s="49">
-        <v>-3.96</v>
+      <c r="T5" s="41">
+        <v>-3.89</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000722</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -6181.92万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>6.98</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="57">
         <v>2.81</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="58">
         <v>-4.61</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="59">
         <v>-11.64</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="54">
         <v>-17.83</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="60">
         <v>-21.09</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="56">
         <v>-23.12</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="62">
         <v>-28.29</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="63">
         <v>-27.67</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="64">
         <v>-26.72</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="65">
         <v>-28.8</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="55">
         <v>-26.94</v>
       </c>
-      <c r="T6" s="60">
-        <v>-18.17</v>
+      <c r="T6" s="61">
+        <v>-18.79</v>
       </c>
     </row>
     <row r="7">
@@ -2177,37 +2177,37 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="73">
+      <c r="I8" s="70">
         <v>40</v>
       </c>
-      <c r="J8" s="66">
+      <c r="J8" s="77">
         <v>20</v>
       </c>
-      <c r="K8" s="67">
+      <c r="K8" s="75">
         <v>0</v>
       </c>
-      <c r="L8" s="68">
+      <c r="L8" s="71">
         <v>0</v>
       </c>
-      <c r="M8" s="70">
+      <c r="M8" s="72">
         <v>0</v>
       </c>
-      <c r="N8" s="76">
+      <c r="N8" s="74">
         <v>0</v>
       </c>
-      <c r="O8" s="74">
+      <c r="O8" s="76">
         <v>0</v>
       </c>
-      <c r="P8" s="71">
+      <c r="P8" s="66">
         <v>0</v>
       </c>
-      <c r="Q8" s="72">
+      <c r="Q8" s="67">
         <v>0</v>
       </c>
-      <c r="R8" s="75">
+      <c r="R8" s="68">
         <v>0</v>
       </c>
-      <c r="S8" s="77">
+      <c r="S8" s="73">
         <v>0</v>
       </c>
       <c r="T8" s="69">
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="89">
+      <c r="I9" s="84">
         <v>-1</v>
       </c>
-      <c r="J9" s="78">
+      <c r="J9" s="79">
         <v>-3.98</v>
       </c>
-      <c r="K9" s="82">
+      <c r="K9" s="80">
         <v>-8.6</v>
       </c>
-      <c r="L9" s="87">
+      <c r="L9" s="81">
         <v>-10.87</v>
       </c>
-      <c r="M9" s="83">
+      <c r="M9" s="87">
         <v>-12.49</v>
       </c>
-      <c r="N9" s="88">
+      <c r="N9" s="82">
         <v>-12.87</v>
       </c>
-      <c r="O9" s="84">
+      <c r="O9" s="85">
         <v>-14.69</v>
       </c>
-      <c r="P9" s="79">
+      <c r="P9" s="83">
         <v>-15.23</v>
       </c>
-      <c r="Q9" s="80">
+      <c r="Q9" s="86">
         <v>-14.38</v>
       </c>
-      <c r="R9" s="85">
+      <c r="R9" s="88">
         <v>-15.16</v>
       </c>
-      <c r="S9" s="81">
+      <c r="S9" s="89">
         <v>-15.24</v>
       </c>
-      <c r="T9" s="86">
-        <v>-10</v>
+      <c r="T9" s="78">
+        <v>-8.56</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/浙江帮/index.xlsx
+++ b/youzi/浙江帮/index.xlsx
@@ -39,73 +39,223 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF26A243"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF65C07A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89CE99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,73 +267,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6EC482"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,127 +303,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -375,102 +459,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -538,6 +526,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>603271</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="7" t="str">
         <v>净卖: -611.78万</v>
       </c>
       <c r="E2">
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>-0.7</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="8">
         <v>1.59</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="11">
         <v>-0.49</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="9">
         <v>-3.9</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="12">
         <v>-5.73</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="10">
         <v>-5.34</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="3">
         <v>-4.71</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="4">
         <v>-5.39</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="5">
         <v>-3.12</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="6">
         <v>-2.73</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="13">
         <v>-3.56</v>
       </c>
-      <c r="T2" s="4">
-        <v>24.17</v>
+      <c r="T2" s="1">
+        <v>22.8</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>000802</v>
       </c>
-      <c r="D3" s="26" t="str">
+      <c r="D3" s="16" t="str">
         <v>净买: 215.00万</v>
       </c>
       <c r="E3">
@@ -1895,40 +1895,40 @@
       <c r="H3">
         <v>-10.05</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="23">
         <v>0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="26">
         <v>-3.35</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="21">
         <v>-6.33</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="17">
         <v>-9.68</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="18">
         <v>-9.5</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="14">
         <v>-7.45</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="24">
         <v>-7.45</v>
       </c>
       <c r="P3" s="19">
         <v>-7.26</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="25">
         <v>-7.08</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="22">
         <v>-7.82</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="20">
         <v>-7.82</v>
       </c>
-      <c r="T3" s="25">
+      <c r="T3" s="15">
         <v>-19.93</v>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300192</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -647.70万</v>
       </c>
       <c r="E4">
@@ -1957,41 +1957,41 @@
       <c r="H4">
         <v>20.01</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="31">
         <v>0</v>
       </c>
       <c r="J4" s="35">
         <v>1.58</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="28">
         <v>-8.92</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="32">
         <v>-6.87</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="36">
         <v>-15.82</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="29">
         <v>-18.33</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="39">
         <v>-20.76</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="27">
         <v>-23.43</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="30">
         <v>-23.39</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="33">
         <v>-23.85</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="34">
         <v>-24.62</v>
       </c>
-      <c r="T4" s="33">
-        <v>-24.35</v>
+      <c r="T4" s="37">
+        <v>-25.4</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>605028</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="42" t="str">
         <v>净买: 256.97万</v>
       </c>
       <c r="E5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>-0.68</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="41">
         <v>-9.39</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="43">
         <v>-13.51</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="44">
         <v>-15.6</v>
       </c>
       <c r="L5" s="50">
         <v>-16.09</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="47">
         <v>-10.3</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="45">
         <v>-10.1</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="51">
         <v>-12.26</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="52">
         <v>-12.39</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="46">
         <v>-11.58</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="40">
         <v>-12.62</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="48">
         <v>-13.28</v>
       </c>
-      <c r="T5" s="41">
-        <v>-3.89</v>
+      <c r="T5" s="49">
+        <v>-4.51</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000722</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="59" t="str">
         <v>净卖: -6181.92万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>6.98</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="63">
         <v>2.81</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="60">
         <v>-4.61</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="61">
         <v>-11.64</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="56">
         <v>-17.83</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="64">
         <v>-21.09</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="53">
         <v>-23.12</v>
       </c>
       <c r="O6" s="62">
         <v>-28.29</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="65">
         <v>-27.67</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="54">
         <v>-26.72</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="57">
         <v>-28.8</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="58">
         <v>-26.94</v>
       </c>
-      <c r="T6" s="61">
-        <v>-18.79</v>
+      <c r="T6" s="55">
+        <v>-16.48</v>
       </c>
     </row>
     <row r="7">
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="70">
+      <c r="I8" s="67">
         <v>40</v>
       </c>
-      <c r="J8" s="77">
+      <c r="J8" s="74">
         <v>20</v>
       </c>
-      <c r="K8" s="75">
+      <c r="K8" s="71">
         <v>0</v>
       </c>
-      <c r="L8" s="71">
+      <c r="L8" s="68">
         <v>0</v>
       </c>
-      <c r="M8" s="72">
+      <c r="M8" s="75">
         <v>0</v>
       </c>
-      <c r="N8" s="74">
+      <c r="N8" s="72">
         <v>0</v>
       </c>
-      <c r="O8" s="76">
+      <c r="O8" s="69">
         <v>0</v>
       </c>
-      <c r="P8" s="66">
+      <c r="P8" s="76">
         <v>0</v>
       </c>
-      <c r="Q8" s="67">
+      <c r="Q8" s="77">
         <v>0</v>
       </c>
-      <c r="R8" s="68">
+      <c r="R8" s="73">
         <v>0</v>
       </c>
-      <c r="S8" s="73">
+      <c r="S8" s="66">
         <v>0</v>
       </c>
-      <c r="T8" s="69">
+      <c r="T8" s="70">
         <v>20</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="84">
+      <c r="I9" s="82">
         <v>-1</v>
       </c>
-      <c r="J9" s="79">
+      <c r="J9" s="83">
         <v>-3.98</v>
       </c>
-      <c r="K9" s="80">
+      <c r="K9" s="88">
         <v>-8.6</v>
       </c>
-      <c r="L9" s="81">
+      <c r="L9" s="89">
         <v>-10.87</v>
       </c>
-      <c r="M9" s="87">
+      <c r="M9" s="84">
         <v>-12.49</v>
       </c>
-      <c r="N9" s="82">
+      <c r="N9" s="85">
         <v>-12.87</v>
       </c>
-      <c r="O9" s="85">
+      <c r="O9" s="78">
         <v>-14.69</v>
       </c>
-      <c r="P9" s="83">
+      <c r="P9" s="86">
         <v>-15.23</v>
       </c>
-      <c r="Q9" s="86">
+      <c r="Q9" s="87">
         <v>-14.38</v>
       </c>
-      <c r="R9" s="88">
+      <c r="R9" s="79">
         <v>-15.16</v>
       </c>
-      <c r="S9" s="89">
+      <c r="S9" s="80">
         <v>-15.24</v>
       </c>
-      <c r="T9" s="78">
-        <v>-8.56</v>
+      <c r="T9" s="81">
+        <v>-8.7</v>
       </c>
     </row>
   </sheetData>
